--- a/Result/profitability/2345.xlsx
+++ b/Result/profitability/2345.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>9.376250000000001</v>
+        <v>11.25625</v>
       </c>
       <c r="N2" t="n">
-        <v>18.87125</v>
+        <v>18.8475</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>8.815</v>
+        <v>10.275</v>
       </c>
       <c r="N3" t="n">
-        <v>18.215</v>
+        <v>18.09125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.43</v>
       </c>
       <c r="M4" t="n">
-        <v>7.85625</v>
+        <v>9.182499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>17.925</v>
+        <v>17.85875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.05</v>
       </c>
       <c r="M5" t="n">
-        <v>6.703749999999999</v>
+        <v>8.05125</v>
       </c>
       <c r="N5" t="n">
-        <v>17.41125</v>
+        <v>17.6325</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.58875</v>
+        <v>6.31125</v>
       </c>
       <c r="N6" t="n">
-        <v>17.4025</v>
+        <v>17.72</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>3.85875</v>
+        <v>4.4625</v>
       </c>
       <c r="N7" t="n">
-        <v>17.69375</v>
+        <v>17.91875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.24</v>
       </c>
       <c r="M8" t="n">
-        <v>2.02</v>
+        <v>2.6275</v>
       </c>
       <c r="N8" t="n">
-        <v>18.03375</v>
+        <v>18.0525</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>95538</v>
+      </c>
+      <c r="D75" t="n">
+        <v>76720</v>
+      </c>
+      <c r="E75" t="n">
+        <v>18817</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="G75" t="n">
+        <v>14331</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.00%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>237</v>
+      </c>
+      <c r="J75" t="n">
+        <v>14568</v>
+      </c>
+      <c r="K75" t="n">
+        <v>11053</v>
+      </c>
+      <c r="L75" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="M75" t="n">
+        <v>11.8325</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.13125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>4.860000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3257372654155497</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.1499999999999986</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.007672634271099765</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.197777777777778</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.09871723368655871</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
